--- a/docs/templates/plantilla-usuarios.xlsx
+++ b/docs/templates/plantilla-usuarios.xlsx
@@ -599,7 +599,7 @@
         <v>Versión de plantilla</v>
       </c>
       <c r="B10" s="1" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="str">
